--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-12-2025.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>£1096.66</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-thermaclass-cavity-wall-21-140mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
